--- a/Train_A_Skill/Level1_Skill_Horizontal_BentArmPush_HighLizardCrawlPushUp.xlsx
+++ b/Train_A_Skill/Level1_Skill_Horizontal_BentArmPush_HighLizardCrawlPushUp.xlsx
@@ -93,7 +93,7 @@
       <sz val="8"/>
     </font>
   </fonts>
-  <fills count="6">
+  <fills count="7">
     <fill>
       <patternFill/>
     </fill>
@@ -117,6 +117,11 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="FFFFE599"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="FFEAF6E1"/>
       </patternFill>
     </fill>
@@ -133,7 +138,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="14">
+  <cellXfs count="15">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -162,16 +167,19 @@
     <xf numFmtId="0" fontId="9" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="5" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="6" fillId="5" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="5" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="10" fillId="6" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="6" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="5" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="11" fillId="6" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="5" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="9" fillId="6" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -539,6 +547,180 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
+  <dimension ref="A1:F10"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="11" customWidth="1" min="1" max="1"/>
+    <col width="34" customWidth="1" min="2" max="2"/>
+    <col width="30" customWidth="1" min="3" max="3"/>
+    <col width="16" customWidth="1" min="4" max="4"/>
+    <col width="8.710000000000001" customWidth="1" min="5" max="5"/>
+    <col width="19" customWidth="1" min="6" max="6"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="31.5" customHeight="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>TRAIN A SKILL — LEVEL 1  ·  HIGH LIZARD CRAWL WITH PUSH-UP  ·  PHASE 1</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="30" customHeight="1">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>Self-paced — stay on each exercise until the standard is earned. Train inside the PRESCRIPTION range; the top of the range is the STANDARD. Phase 1 = the 0 exercises + the grade 1 exercises. ◇ PICK 1 = choose one. Every cell is a per-set prescription.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="21.75" customHeight="1">
+      <c r="A4" s="3" t="n"/>
+      <c r="B4" s="3" t="inlineStr">
+        <is>
+          <t>EXERCISE</t>
+        </is>
+      </c>
+      <c r="C4" s="3" t="inlineStr">
+        <is>
+          <t>STANDARD</t>
+        </is>
+      </c>
+      <c r="D4" s="3" t="inlineStr">
+        <is>
+          <t>PRESCRIPTION</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="18.75" customHeight="1">
+      <c r="A5" s="4" t="inlineStr">
+        <is>
+          <t>PHASE 1 · HORIZONTAL BENT ARM PUSH · 3 sets</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="15" customHeight="1">
+      <c r="A6" s="5" t="inlineStr">
+        <is>
+          <t>◇  PICK 1  —  interchangeable, choose one</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="24" customHeight="1">
+      <c r="A7" s="6" t="inlineStr">
+        <is>
+          <t>○  1</t>
+        </is>
+      </c>
+      <c r="B7" s="7" t="inlineStr">
+        <is>
+          <t>Seated push-up</t>
+        </is>
+      </c>
+      <c r="C7" s="8" t="inlineStr">
+        <is>
+          <t>15 reps each side</t>
+        </is>
+      </c>
+      <c r="D7" s="9" t="inlineStr">
+        <is>
+          <t>5–15 reps</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="24" customHeight="1">
+      <c r="A8" s="6" t="inlineStr">
+        <is>
+          <t>○  1</t>
+        </is>
+      </c>
+      <c r="B8" s="7" t="inlineStr">
+        <is>
+          <t>Eccentric Kneeling Pushup</t>
+        </is>
+      </c>
+      <c r="C8" s="8" t="inlineStr">
+        <is>
+          <t>15 reps</t>
+        </is>
+      </c>
+      <c r="D8" s="9" t="inlineStr">
+        <is>
+          <t>5–15 reps</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" ht="24" customHeight="1">
+      <c r="A9" s="6" t="inlineStr">
+        <is>
+          <t>○  0</t>
+        </is>
+      </c>
+      <c r="B9" s="7" t="inlineStr">
+        <is>
+          <t>DB Push</t>
+        </is>
+      </c>
+      <c r="C9" s="8" t="inlineStr">
+        <is>
+          <t>10 reps at 60% bodyweight</t>
+        </is>
+      </c>
+      <c r="D9" s="9" t="inlineStr">
+        <is>
+          <t>5–10 reps @ 25–40% BW</t>
+        </is>
+      </c>
+    </row>
+    <row r="10" ht="24" customHeight="1">
+      <c r="A10" s="6" t="inlineStr">
+        <is>
+          <t>○  0</t>
+        </is>
+      </c>
+      <c r="B10" s="7" t="inlineStr">
+        <is>
+          <t>Cable Chest Press</t>
+        </is>
+      </c>
+      <c r="C10" s="8" t="inlineStr">
+        <is>
+          <t>10 reps at 20% bodyweight</t>
+        </is>
+      </c>
+      <c r="D10" s="9" t="inlineStr">
+        <is>
+          <t>5–10 reps @ 7.5–10% BW</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="9">
+    <mergeCell ref="A2:F2"/>
+    <mergeCell ref="A1:F1"/>
+    <mergeCell ref="D4:F4"/>
+    <mergeCell ref="A5:F5"/>
+    <mergeCell ref="A6:F6"/>
+    <mergeCell ref="D9:F9"/>
+    <mergeCell ref="D7:F7"/>
+    <mergeCell ref="D8:F8"/>
+    <mergeCell ref="D10:F10"/>
+  </mergeCells>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B7" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B8" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B9" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B10" r:id="rId4"/>
+  </hyperlinks>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageSetup orientation="landscape" fitToHeight="0" fitToWidth="1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr fitToPage="1"/>
+  </sheetPr>
   <dimension ref="A1:F11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
@@ -553,14 +735,14 @@
     <row r="1" ht="31.5" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>TRAIN A SKILL — LEVEL 1  ·  HIGH LIZARD CRAWL WITH PUSH-UP  ·  PHASE 1</t>
+          <t>TRAIN A SKILL — LEVEL 1  ·  HIGH LIZARD CRAWL WITH PUSH-UP  ·  PHASE 2</t>
         </is>
       </c>
     </row>
     <row r="2" ht="30" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Self-paced — stay on each exercise until the standard is earned. Train inside the PRESCRIPTION range; the top of the range is the STANDARD. Phase 1 = the 0 exercises + the grade 1 exercises. ◇ PICK 1 = choose one. Every cell is a per-set prescription.</t>
+          <t>Self-paced — stay on each exercise until the standard is earned. Train inside the PRESCRIPTION range; the top of the range is the STANDARD. Phase 2 = the 0 exercises + the grade 2 exercises. ◇ PICK 1 = choose one. Every cell is a per-set prescription.</t>
         </is>
       </c>
     </row>
@@ -585,7 +767,7 @@
     <row r="5" ht="18.75" customHeight="1">
       <c r="A5" s="4" t="inlineStr">
         <is>
-          <t>PHASE 1 · HORIZONTAL BENT ARM PUSH · 3 sets</t>
+          <t>PHASE 2 · HORIZONTAL BENT ARM PUSH · 3 sets</t>
         </is>
       </c>
     </row>
@@ -599,17 +781,17 @@
     <row r="7" ht="24" customHeight="1">
       <c r="A7" s="6" t="inlineStr">
         <is>
-          <t>○  1</t>
+          <t>○  2</t>
         </is>
       </c>
       <c r="B7" s="7" t="inlineStr">
         <is>
-          <t>Seated push-up</t>
+          <t>Kneeling push-ups</t>
         </is>
       </c>
       <c r="C7" s="8" t="inlineStr">
         <is>
-          <t>15 reps each side</t>
+          <t>15 reps</t>
         </is>
       </c>
       <c r="D7" s="9" t="inlineStr">
@@ -621,44 +803,44 @@
     <row r="8" ht="24" customHeight="1">
       <c r="A8" s="6" t="inlineStr">
         <is>
-          <t>○  1</t>
+          <t>○  2</t>
         </is>
       </c>
       <c r="B8" s="7" t="inlineStr">
         <is>
-          <t>Eccentric Kneeling Pushup</t>
+          <t>Rotational Kneeling Pushup</t>
         </is>
       </c>
       <c r="C8" s="8" t="inlineStr">
         <is>
-          <t>15 reps</t>
+          <t>10 reps each side</t>
         </is>
       </c>
       <c r="D8" s="9" t="inlineStr">
         <is>
-          <t>5–15 reps</t>
+          <t>6–10 reps</t>
         </is>
       </c>
     </row>
     <row r="9" ht="24" customHeight="1">
       <c r="A9" s="6" t="inlineStr">
         <is>
-          <t>○  1</t>
+          <t>○  2</t>
         </is>
       </c>
       <c r="B9" s="7" t="inlineStr">
         <is>
-          <t>Kneeling push-ups</t>
+          <t>Eccentric Incline Ring Push-ups</t>
         </is>
       </c>
       <c r="C9" s="8" t="inlineStr">
         <is>
-          <t>15 reps</t>
+          <t>10 reps at a 45° angle</t>
         </is>
       </c>
       <c r="D9" s="9" t="inlineStr">
         <is>
-          <t>5–15 reps</t>
+          <t>6–10 reps</t>
         </is>
       </c>
     </row>
@@ -680,7 +862,7 @@
       </c>
       <c r="D10" s="9" t="inlineStr">
         <is>
-          <t>5–10 reps @ 25–40% BW</t>
+          <t>5–10 reps @ 45–50% BW</t>
         </is>
       </c>
     </row>
@@ -702,7 +884,7 @@
       </c>
       <c r="D11" s="9" t="inlineStr">
         <is>
-          <t>5–10 reps @ 7.5–10% BW</t>
+          <t>5–10 reps @ 12.5–15% BW</t>
         </is>
       </c>
     </row>
@@ -731,13 +913,13 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:F13"/>
+  <dimension ref="A1:F16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="11" customWidth="1" min="1" max="1"/>
@@ -751,14 +933,14 @@
     <row r="1" ht="31.5" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>TRAIN A SKILL — LEVEL 1  ·  HIGH LIZARD CRAWL WITH PUSH-UP  ·  PHASE 2</t>
+          <t>TRAIN A SKILL — LEVEL 1  ·  HIGH LIZARD CRAWL WITH PUSH-UP  ·  PHASE 3</t>
         </is>
       </c>
     </row>
     <row r="2" ht="30" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Self-paced — stay on each exercise until the standard is earned. Train inside the PRESCRIPTION range; the top of the range is the STANDARD. Phase 2 = the 0 exercises + the grade 2 exercises. ◇ PICK 1 = choose one. Every cell is a per-set prescription.</t>
+          <t>Self-paced — stay on each exercise until the standard is earned. Train inside the PRESCRIPTION range; the top of the range is the STANDARD. Phase 3 = the 0 exercises + the grade 3 exercises. ◇ PICK 1 = choose one. Every cell is a per-set prescription.</t>
         </is>
       </c>
     </row>
@@ -783,7 +965,7 @@
     <row r="5" ht="18.75" customHeight="1">
       <c r="A5" s="4" t="inlineStr">
         <is>
-          <t>PHASE 2 · HORIZONTAL BENT ARM PUSH · 3 sets</t>
+          <t>PHASE 3 · HORIZONTAL BENT ARM PUSH · 3 sets</t>
         </is>
       </c>
     </row>
@@ -797,162 +979,229 @@
     <row r="7" ht="24" customHeight="1">
       <c r="A7" s="6" t="inlineStr">
         <is>
-          <t>○  2</t>
+          <t>○  3</t>
         </is>
       </c>
       <c r="B7" s="7" t="inlineStr">
         <is>
-          <t>Rotational Kneeling Pushup</t>
+          <t>Incline Ring Push-up</t>
         </is>
       </c>
       <c r="C7" s="8" t="inlineStr">
         <is>
-          <t>10 reps each side</t>
+          <t>15 reps at a 45° angle</t>
         </is>
       </c>
       <c r="D7" s="9" t="inlineStr">
         <is>
-          <t>6–10 reps</t>
+          <t>5–15 reps</t>
         </is>
       </c>
     </row>
     <row r="8" ht="24" customHeight="1">
       <c r="A8" s="6" t="inlineStr">
         <is>
-          <t>○  2</t>
+          <t>○  3</t>
         </is>
       </c>
       <c r="B8" s="7" t="inlineStr">
         <is>
-          <t>Eccentric Incline Ring Push-ups</t>
+          <t>Eccentric push-up + kneeling concentric</t>
         </is>
       </c>
       <c r="C8" s="8" t="inlineStr">
         <is>
-          <t>10 reps at a 45° angle</t>
+          <t>15 reps</t>
         </is>
       </c>
       <c r="D8" s="9" t="inlineStr">
         <is>
-          <t>6–10 reps</t>
+          <t>5–15 reps</t>
         </is>
       </c>
     </row>
     <row r="9" ht="24" customHeight="1">
       <c r="A9" s="6" t="inlineStr">
         <is>
-          <t>○  2</t>
+          <t>○  3</t>
         </is>
       </c>
       <c r="B9" s="7" t="inlineStr">
         <is>
-          <t>Incline Ring Push-up</t>
+          <t>Single arm seated push-up</t>
         </is>
       </c>
       <c r="C9" s="8" t="inlineStr">
         <is>
-          <t>15 reps at a 45° angle</t>
+          <t>10 reps each side</t>
         </is>
       </c>
       <c r="D9" s="9" t="inlineStr">
         <is>
-          <t>5–15 reps</t>
+          <t>6–10 reps</t>
         </is>
       </c>
     </row>
     <row r="10" ht="24" customHeight="1">
       <c r="A10" s="6" t="inlineStr">
         <is>
-          <t>○  2</t>
+          <t>○  3</t>
         </is>
       </c>
       <c r="B10" s="7" t="inlineStr">
         <is>
-          <t>Eccentric push-up + kneeling concentric</t>
+          <t>Bent arm push-up hold</t>
         </is>
       </c>
       <c r="C10" s="8" t="inlineStr">
         <is>
+          <t>30s hold</t>
+        </is>
+      </c>
+      <c r="D10" s="9" t="inlineStr">
+        <is>
+          <t>15–30s</t>
+        </is>
+      </c>
+    </row>
+    <row r="11" ht="24" customHeight="1">
+      <c r="A11" s="10" t="inlineStr">
+        <is>
+          <t>○  4</t>
+        </is>
+      </c>
+      <c r="B11" s="7" t="inlineStr">
+        <is>
+          <t>2 Arm Pushup</t>
+        </is>
+      </c>
+      <c r="C11" s="8" t="inlineStr">
+        <is>
           <t>15 reps</t>
         </is>
       </c>
-      <c r="D10" s="9" t="inlineStr">
+      <c r="D11" s="9" t="inlineStr">
         <is>
           <t>5–15 reps</t>
         </is>
       </c>
     </row>
-    <row r="11" ht="24" customHeight="1">
-      <c r="A11" s="6" t="inlineStr">
-        <is>
-          <t>○  2</t>
-        </is>
-      </c>
-      <c r="B11" s="7" t="inlineStr">
-        <is>
-          <t>Single arm seated push-up</t>
-        </is>
-      </c>
-      <c r="C11" s="8" t="inlineStr">
+    <row r="12" ht="24" customHeight="1">
+      <c r="A12" s="10" t="inlineStr">
+        <is>
+          <t>○  4</t>
+        </is>
+      </c>
+      <c r="B12" s="7" t="inlineStr">
+        <is>
+          <t>2 Arm Rotational Pushup</t>
+        </is>
+      </c>
+      <c r="C12" s="8" t="inlineStr">
         <is>
           <t>10 reps each side</t>
         </is>
       </c>
-      <c r="D11" s="9" t="inlineStr">
+      <c r="D12" s="9" t="inlineStr">
         <is>
           <t>6–10 reps</t>
         </is>
       </c>
     </row>
-    <row r="12" ht="24" customHeight="1">
-      <c r="A12" s="6" t="inlineStr">
+    <row r="13" ht="24" customHeight="1">
+      <c r="A13" s="10" t="inlineStr">
+        <is>
+          <t>○  4</t>
+        </is>
+      </c>
+      <c r="B13" s="7" t="inlineStr">
+        <is>
+          <t>Rotational Lunge Push-up-two arms</t>
+        </is>
+      </c>
+      <c r="C13" s="8" t="inlineStr">
+        <is>
+          <t>10 reps each side</t>
+        </is>
+      </c>
+      <c r="D13" s="9" t="inlineStr">
+        <is>
+          <t>6–10 reps</t>
+        </is>
+      </c>
+    </row>
+    <row r="14" ht="24" customHeight="1">
+      <c r="A14" s="10" t="inlineStr">
+        <is>
+          <t>○  4</t>
+        </is>
+      </c>
+      <c r="B14" s="7" t="inlineStr">
+        <is>
+          <t>QDR Push-ups</t>
+        </is>
+      </c>
+      <c r="C14" s="8" t="inlineStr">
+        <is>
+          <t>10 reps, 2s hold each, knees off floor</t>
+        </is>
+      </c>
+      <c r="D14" s="9" t="inlineStr">
+        <is>
+          <t>6–10 total reps  (3–5 each side)</t>
+        </is>
+      </c>
+    </row>
+    <row r="15" ht="24" customHeight="1">
+      <c r="A15" s="6" t="inlineStr">
         <is>
           <t>○  0</t>
         </is>
       </c>
-      <c r="B12" s="7" t="inlineStr">
+      <c r="B15" s="7" t="inlineStr">
         <is>
           <t>DB Push</t>
         </is>
       </c>
-      <c r="C12" s="8" t="inlineStr">
+      <c r="C15" s="8" t="inlineStr">
         <is>
           <t>10 reps at 60% bodyweight</t>
         </is>
       </c>
-      <c r="D12" s="9" t="inlineStr">
-        <is>
-          <t>5–10 reps @ 45–50% BW</t>
-        </is>
-      </c>
-    </row>
-    <row r="13" ht="24" customHeight="1">
-      <c r="A13" s="6" t="inlineStr">
+      <c r="D15" s="9" t="inlineStr">
+        <is>
+          <t>5–10 reps @ 55–60% BW</t>
+        </is>
+      </c>
+    </row>
+    <row r="16" ht="24" customHeight="1">
+      <c r="A16" s="6" t="inlineStr">
         <is>
           <t>○  0</t>
         </is>
       </c>
-      <c r="B13" s="7" t="inlineStr">
+      <c r="B16" s="7" t="inlineStr">
         <is>
           <t>Cable Chest Press</t>
         </is>
       </c>
-      <c r="C13" s="8" t="inlineStr">
+      <c r="C16" s="8" t="inlineStr">
         <is>
           <t>10 reps at 20% bodyweight</t>
         </is>
       </c>
-      <c r="D13" s="9" t="inlineStr">
-        <is>
-          <t>5–10 reps @ 12.5–15% BW</t>
+      <c r="D16" s="9" t="inlineStr">
+        <is>
+          <t>5–10 reps @ 17.5–20% BW</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="12">
+  <mergeCells count="15">
     <mergeCell ref="A2:F2"/>
     <mergeCell ref="D11:F11"/>
     <mergeCell ref="D13:F13"/>
+    <mergeCell ref="D14:F14"/>
     <mergeCell ref="A1:F1"/>
     <mergeCell ref="D4:F4"/>
     <mergeCell ref="A5:F5"/>
@@ -961,6 +1210,8 @@
     <mergeCell ref="D9:F9"/>
     <mergeCell ref="D7:F7"/>
     <mergeCell ref="D8:F8"/>
+    <mergeCell ref="D15:F15"/>
+    <mergeCell ref="D16:F16"/>
     <mergeCell ref="D10:F10"/>
   </mergeCells>
   <hyperlinks>
@@ -971,252 +1222,9 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B11" r:id="rId5"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B12" r:id="rId6"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B13" r:id="rId7"/>
-  </hyperlinks>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-  <pageSetup orientation="landscape" fitToHeight="0" fitToWidth="1"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr fitToPage="1"/>
-  </sheetPr>
-  <dimension ref="A1:F13"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="11" customWidth="1" min="1" max="1"/>
-    <col width="34" customWidth="1" min="2" max="2"/>
-    <col width="30" customWidth="1" min="3" max="3"/>
-    <col width="16" customWidth="1" min="4" max="4"/>
-    <col width="8.710000000000001" customWidth="1" min="5" max="5"/>
-    <col width="19" customWidth="1" min="6" max="6"/>
-  </cols>
-  <sheetData>
-    <row r="1" ht="31.5" customHeight="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>TRAIN A SKILL — LEVEL 1  ·  HIGH LIZARD CRAWL WITH PUSH-UP  ·  PHASE 3</t>
-        </is>
-      </c>
-    </row>
-    <row r="2" ht="30" customHeight="1">
-      <c r="A2" s="2" t="inlineStr">
-        <is>
-          <t>Self-paced — stay on each exercise until the standard is earned. Train inside the PRESCRIPTION range; the top of the range is the STANDARD. Phase 3 = the 0 exercises + the grade 3 exercises. ◇ PICK 1 = choose one. Every cell is a per-set prescription.</t>
-        </is>
-      </c>
-    </row>
-    <row r="4" ht="21.75" customHeight="1">
-      <c r="A4" s="3" t="n"/>
-      <c r="B4" s="3" t="inlineStr">
-        <is>
-          <t>EXERCISE</t>
-        </is>
-      </c>
-      <c r="C4" s="3" t="inlineStr">
-        <is>
-          <t>STANDARD</t>
-        </is>
-      </c>
-      <c r="D4" s="3" t="inlineStr">
-        <is>
-          <t>PRESCRIPTION</t>
-        </is>
-      </c>
-    </row>
-    <row r="5" ht="18.75" customHeight="1">
-      <c r="A5" s="4" t="inlineStr">
-        <is>
-          <t>PHASE 3 · HORIZONTAL BENT ARM PUSH · 3 sets</t>
-        </is>
-      </c>
-    </row>
-    <row r="6" ht="15" customHeight="1">
-      <c r="A6" s="5" t="inlineStr">
-        <is>
-          <t>◇  PICK 1  —  interchangeable, choose one</t>
-        </is>
-      </c>
-    </row>
-    <row r="7" ht="24" customHeight="1">
-      <c r="A7" s="6" t="inlineStr">
-        <is>
-          <t>○  3</t>
-        </is>
-      </c>
-      <c r="B7" s="7" t="inlineStr">
-        <is>
-          <t>Bent arm push-up hold</t>
-        </is>
-      </c>
-      <c r="C7" s="8" t="inlineStr">
-        <is>
-          <t>30s hold</t>
-        </is>
-      </c>
-      <c r="D7" s="9" t="inlineStr">
-        <is>
-          <t>15–30s</t>
-        </is>
-      </c>
-    </row>
-    <row r="8" ht="24" customHeight="1">
-      <c r="A8" s="6" t="inlineStr">
-        <is>
-          <t>○  3</t>
-        </is>
-      </c>
-      <c r="B8" s="7" t="inlineStr">
-        <is>
-          <t>2 Arm Pushup</t>
-        </is>
-      </c>
-      <c r="C8" s="8" t="inlineStr">
-        <is>
-          <t>15 reps</t>
-        </is>
-      </c>
-      <c r="D8" s="9" t="inlineStr">
-        <is>
-          <t>5–15 reps</t>
-        </is>
-      </c>
-    </row>
-    <row r="9" ht="24" customHeight="1">
-      <c r="A9" s="6" t="inlineStr">
-        <is>
-          <t>○  3</t>
-        </is>
-      </c>
-      <c r="B9" s="7" t="inlineStr">
-        <is>
-          <t>2 Arm Rotational Pushup</t>
-        </is>
-      </c>
-      <c r="C9" s="8" t="inlineStr">
-        <is>
-          <t>10 reps each side</t>
-        </is>
-      </c>
-      <c r="D9" s="9" t="inlineStr">
-        <is>
-          <t>6–10 reps</t>
-        </is>
-      </c>
-    </row>
-    <row r="10" ht="24" customHeight="1">
-      <c r="A10" s="6" t="inlineStr">
-        <is>
-          <t>○  3</t>
-        </is>
-      </c>
-      <c r="B10" s="7" t="inlineStr">
-        <is>
-          <t>Rotational Lunge Push-up-two arms</t>
-        </is>
-      </c>
-      <c r="C10" s="8" t="inlineStr">
-        <is>
-          <t>10 reps each side</t>
-        </is>
-      </c>
-      <c r="D10" s="9" t="inlineStr">
-        <is>
-          <t>6–10 reps</t>
-        </is>
-      </c>
-    </row>
-    <row r="11" ht="24" customHeight="1">
-      <c r="A11" s="6" t="inlineStr">
-        <is>
-          <t>○  3</t>
-        </is>
-      </c>
-      <c r="B11" s="7" t="inlineStr">
-        <is>
-          <t>QDR Push-ups</t>
-        </is>
-      </c>
-      <c r="C11" s="8" t="inlineStr">
-        <is>
-          <t>10 reps, 2s hold each, knees off floor</t>
-        </is>
-      </c>
-      <c r="D11" s="9" t="inlineStr">
-        <is>
-          <t>6–10 total reps  (3–5 each side)</t>
-        </is>
-      </c>
-    </row>
-    <row r="12" ht="24" customHeight="1">
-      <c r="A12" s="6" t="inlineStr">
-        <is>
-          <t>○  0</t>
-        </is>
-      </c>
-      <c r="B12" s="7" t="inlineStr">
-        <is>
-          <t>DB Push</t>
-        </is>
-      </c>
-      <c r="C12" s="8" t="inlineStr">
-        <is>
-          <t>10 reps at 60% bodyweight</t>
-        </is>
-      </c>
-      <c r="D12" s="9" t="inlineStr">
-        <is>
-          <t>5–10 reps @ 55–60% BW</t>
-        </is>
-      </c>
-    </row>
-    <row r="13" ht="24" customHeight="1">
-      <c r="A13" s="6" t="inlineStr">
-        <is>
-          <t>○  0</t>
-        </is>
-      </c>
-      <c r="B13" s="7" t="inlineStr">
-        <is>
-          <t>Cable Chest Press</t>
-        </is>
-      </c>
-      <c r="C13" s="8" t="inlineStr">
-        <is>
-          <t>10 reps at 20% bodyweight</t>
-        </is>
-      </c>
-      <c r="D13" s="9" t="inlineStr">
-        <is>
-          <t>5–10 reps @ 17.5–20% BW</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <mergeCells count="12">
-    <mergeCell ref="A2:F2"/>
-    <mergeCell ref="D11:F11"/>
-    <mergeCell ref="D13:F13"/>
-    <mergeCell ref="A1:F1"/>
-    <mergeCell ref="D4:F4"/>
-    <mergeCell ref="A5:F5"/>
-    <mergeCell ref="D12:F12"/>
-    <mergeCell ref="A6:F6"/>
-    <mergeCell ref="D9:F9"/>
-    <mergeCell ref="D7:F7"/>
-    <mergeCell ref="D8:F8"/>
-    <mergeCell ref="D10:F10"/>
-  </mergeCells>
-  <hyperlinks>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B7" r:id="rId1"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B8" r:id="rId2"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B9" r:id="rId3"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B10" r:id="rId4"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B11" r:id="rId5"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B12" r:id="rId6"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B13" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B14" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B15" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B16" r:id="rId10"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup orientation="landscape" fitToHeight="0" fitToWidth="1"/>
@@ -1280,44 +1288,44 @@
       </c>
     </row>
     <row r="6" ht="24" customHeight="1">
-      <c r="A6" s="10" t="inlineStr">
+      <c r="A6" s="11" t="inlineStr">
         <is>
           <t>✦</t>
         </is>
       </c>
-      <c r="B6" s="11" t="inlineStr">
+      <c r="B6" s="12" t="inlineStr">
         <is>
           <t>TEST: High Lizard Crawl-with push-up</t>
         </is>
       </c>
-      <c r="C6" s="12" t="inlineStr">
+      <c r="C6" s="13" t="inlineStr">
         <is>
           <t>PASS: 12 reps full range</t>
         </is>
       </c>
-      <c r="D6" s="13" t="inlineStr">
+      <c r="D6" s="14" t="inlineStr">
         <is>
           <t>6–12 reps · 2 sets</t>
         </is>
       </c>
     </row>
     <row r="7" ht="24" customHeight="1">
-      <c r="A7" s="10" t="inlineStr">
+      <c r="A7" s="11" t="inlineStr">
         <is>
           <t>✦</t>
         </is>
       </c>
-      <c r="B7" s="11" t="inlineStr">
+      <c r="B7" s="12" t="inlineStr">
         <is>
           <t>TEST: Rotational High Lizard Crawl-with push-up</t>
         </is>
       </c>
-      <c r="C7" s="12" t="inlineStr">
+      <c r="C7" s="13" t="inlineStr">
         <is>
           <t>PASS: 12 reps full range</t>
         </is>
       </c>
-      <c r="D7" s="13" t="inlineStr">
+      <c r="D7" s="14" t="inlineStr">
         <is>
           <t>6–12 reps · 2 sets</t>
         </is>
